--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675BFBA7-8D01-4E12-AE84-40D22BAE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5119A9-01B9-47A0-98BE-973A4DAA0967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="20370" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -325,6 +325,18 @@
   </si>
   <si>
     <t>fieldEffectiveDate__c</t>
+  </si>
+  <si>
+    <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>Prince George</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>fieldPaymentAddressCountry__c</t>
   </si>
 </sst>
 </file>
@@ -473,7 +485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -489,14 +501,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,12 +517,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -804,141 +811,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>65</v>
+      <c r="C7" s="18" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -954,32 +961,32 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -990,7 +997,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1001,7 +1008,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1012,7 +1019,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1023,7 +1030,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1041,35 +1048,35 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -1080,7 +1087,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1091,7 +1098,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1102,7 +1109,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1113,7 +1120,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1124,7 +1131,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1142,10 +1149,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1178,9 +1185,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1214,9 +1221,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1249,9 +1256,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1284,10 +1291,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1331,10 +1338,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1426,10 +1433,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1485,20 +1492,20 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1531,7 +1538,7 @@
       <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1539,10 +1546,10 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1550,10 +1557,10 @@
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1566,28 +1573,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
@@ -1595,10 +1602,10 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C3">
@@ -1613,10 +1620,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1683,10 +1690,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1763,109 +1770,120 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="28" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="28" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="C7" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C8" s="19">
         <v>20301</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="28" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1878,125 +1896,125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>20301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -2018,153 +2036,153 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2178,116 +2196,127 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="19">
         <v>20301</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>1234</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2298,9 +2327,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2393,11 +2422,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2488,7 +2517,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2542,32 +2571,32 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2578,7 +2607,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2589,7 +2618,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2600,7 +2629,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -2611,7 +2640,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -2622,13 +2651,13 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>49</v>
       </c>
     </row>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675BFBA7-8D01-4E12-AE84-40D22BAE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019DA889-2125-47BB-B9C7-3D4294ED4EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="20370" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -168,9 +168,6 @@
     <t>IND: INDIA</t>
   </si>
   <si>
-    <t>fieldPrimaryRepPrefix__c</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
@@ -225,9 +222,6 @@
     <t>fieldOrganizationTypeSInglePicklist__c</t>
   </si>
   <si>
-    <t>For Profit Organizations</t>
-  </si>
-  <si>
     <t>fieldWebsite__c</t>
   </si>
   <si>
@@ -261,21 +255,6 @@
     <t>fieldPaymentAddressVendorLocation__c</t>
   </si>
   <si>
-    <t>fieldSameAsOrganizationAddress__c</t>
-  </si>
-  <si>
-    <t>fieldPaymentAddressLine1__c</t>
-  </si>
-  <si>
-    <t>fieldPaymentAddressCity__c</t>
-  </si>
-  <si>
-    <t>fieldPaymentAddressState__c</t>
-  </si>
-  <si>
-    <t>fieldPaymentAddressZipCode__c</t>
-  </si>
-  <si>
     <t>1000 Defense Pentagon</t>
   </si>
   <si>
@@ -285,9 +264,6 @@
     <t>DC</t>
   </si>
   <si>
-    <t>fieldPaymentAddressZipCode4__c</t>
-  </si>
-  <si>
     <t>fieldPrimaryRepAddress1__c</t>
   </si>
   <si>
@@ -312,9 +288,6 @@
     <t>Automation Representative</t>
   </si>
   <si>
-    <t>fieldPrimaryRepEmail__c</t>
-  </si>
-  <si>
     <t>AutomationInternal@yopmail.com</t>
   </si>
   <si>
@@ -325,6 +298,93 @@
   </si>
   <si>
     <t>fieldEffectiveDate__c</t>
+  </si>
+  <si>
+    <t>SameAsOrganizationAddress__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressLine1__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressCity__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressState__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressZipCode__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressZipCode4__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressVendorLocation__c</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>OrganizationTypeSInglePicklist__c</t>
+  </si>
+  <si>
+    <t>OrgnizationPhoneNumber__c</t>
+  </si>
+  <si>
+    <t>Website__c</t>
+  </si>
+  <si>
+    <t>OrganizationStreetAddress__c</t>
+  </si>
+  <si>
+    <t>County__c</t>
+  </si>
+  <si>
+    <t>OrganizationCityAddress__c</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>StateDropdownList__c</t>
+  </si>
+  <si>
+    <t>OrganizationsCountry__c</t>
+  </si>
+  <si>
+    <t>OrganizationZipCode__c</t>
+  </si>
+  <si>
+    <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>PrimaryRepPrefix__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepFirstName__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepLastName__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepAddress1__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepCity__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepState__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepZipCode__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepCountry__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepPhone__c</t>
+  </si>
+  <si>
+    <t>PrimaryRepEmail__c</t>
   </si>
 </sst>
 </file>
@@ -473,7 +533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -489,14 +549,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,12 +565,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -804,141 +859,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="19">
+        <v>20171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="22">
-        <v>20171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -954,32 +1009,32 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -990,7 +1045,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1001,7 +1056,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1012,25 +1067,25 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1041,35 +1096,35 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -1080,7 +1135,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1091,7 +1146,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1102,33 +1157,33 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1142,10 +1197,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1178,9 +1233,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1214,9 +1269,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1249,9 +1304,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1284,10 +1339,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1331,10 +1386,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1411,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1426,10 +1481,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1451,7 +1506,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1485,20 +1540,20 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1510,7 +1565,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1531,7 +1586,7 @@
       <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1539,10 +1594,10 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1550,10 +1605,10 @@
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1566,40 +1621,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>62</v>
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>92</v>
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1613,10 +1668,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1683,10 +1738,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1764,108 +1819,108 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="C3" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>87</v>
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="22" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="19">
+        <v>20301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="22" t="s">
+      <c r="C8" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="22">
-        <v>20301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1878,132 +1933,132 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>81</v>
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="22" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="19">
+        <v>20301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="22">
-        <v>20301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2018,153 +2073,153 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>90</v>
+      <c r="C2" s="19" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C5" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C6" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C11" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="19">
+        <v>20171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="22">
-        <v>20171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2179,115 +2234,115 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="A2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="19">
         <v>20301</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="22">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="19">
         <v>1234</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="22" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2298,9 +2353,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2378,7 +2433,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2393,11 +2448,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2419,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2463,7 +2518,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2488,7 +2543,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2528,10 +2583,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
         <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2542,32 +2597,32 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2578,7 +2633,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2589,7 +2644,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2600,36 +2655,36 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>49</v>
+      <c r="C8" s="13" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019DA889-2125-47BB-B9C7-3D4294ED4EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D8D2BC-2631-47F2-AFCE-475158A62A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="114">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>PrimaryRepEmail__c</t>
+  </si>
+  <si>
+    <t>Prince George</t>
   </si>
 </sst>
 </file>
@@ -939,7 +942,7 @@
         <v>96</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D8D2BC-2631-47F2-AFCE-475158A62A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A9E19-6727-4E19-B817-63CFE77BDB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="115">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -297,9 +297,6 @@
     <t>Automation Runtime</t>
   </si>
   <si>
-    <t>fieldEffectiveDate__c</t>
-  </si>
-  <si>
     <t>SameAsOrganizationAddress__c</t>
   </si>
   <si>
@@ -388,6 +385,12 @@
   </si>
   <si>
     <t>Prince George</t>
+  </si>
+  <si>
+    <t>ParentOrganization__c</t>
+  </si>
+  <si>
+    <t>EffectiveDate__c</t>
   </si>
 </sst>
 </file>
@@ -895,10 +898,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -906,7 +909,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -917,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>59</v>
@@ -928,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -939,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -950,7 +953,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -961,10 +964,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -972,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>67</v>
@@ -983,7 +986,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -994,7 +997,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1646,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
@@ -1657,7 +1660,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1959,7 +1962,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>40</v>
@@ -1970,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>73</v>
@@ -1981,7 +1984,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>43</v>
@@ -1992,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>79</v>
@@ -2003,7 +2006,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>70</v>
@@ -2014,7 +2017,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>71</v>
@@ -2025,7 +2028,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2036,7 +2039,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>67</v>
@@ -2047,7 +2050,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2058,7 +2061,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>80</v>
@@ -2113,7 +2116,7 @@
         <v>57</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2261,7 +2264,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>6</v>
@@ -2274,7 +2277,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>69</v>
@@ -2287,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>70</v>
@@ -2300,10 +2303,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2313,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2326,7 +2329,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2339,7 +2342,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A9E19-6727-4E19-B817-63CFE77BDB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A083106E-C044-425E-BB25-FEE6FA5D66C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -18,23 +18,25 @@
     <sheet name="AuthorizedRepresentativeDetails" sheetId="14" r:id="rId3"/>
     <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId4"/>
     <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId5"/>
-    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId6"/>
-    <sheet name="CreationQ1NO" sheetId="19" r:id="rId7"/>
-    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId8"/>
-    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId9"/>
-    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId10"/>
-    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId11"/>
-    <sheet name="Question1" sheetId="2" r:id="rId12"/>
-    <sheet name="Question2" sheetId="4" r:id="rId13"/>
-    <sheet name="Question1No" sheetId="3" r:id="rId14"/>
-    <sheet name="Question2No" sheetId="5" r:id="rId15"/>
-    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId16"/>
-    <sheet name="OrgAddress" sheetId="7" r:id="rId17"/>
-    <sheet name="OrgProfile" sheetId="8" r:id="rId18"/>
-    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId19"/>
-    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId20"/>
-    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId21"/>
-    <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId22"/>
+    <sheet name="Sheet1" sheetId="24" r:id="rId6"/>
+    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId7"/>
+    <sheet name="CreationQ1NO" sheetId="19" r:id="rId8"/>
+    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId9"/>
+    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId10"/>
+    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId11"/>
+    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId12"/>
+    <sheet name="Question1" sheetId="2" r:id="rId13"/>
+    <sheet name="Question2" sheetId="4" r:id="rId14"/>
+    <sheet name="Question1No" sheetId="3" r:id="rId15"/>
+    <sheet name="Question2No" sheetId="5" r:id="rId16"/>
+    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId17"/>
+    <sheet name="OrgAddress" sheetId="7" r:id="rId18"/>
+    <sheet name="OrgProfile" sheetId="8" r:id="rId19"/>
+    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId20"/>
+    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId21"/>
+    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId22"/>
+    <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId23"/>
+    <sheet name="Individual_PrimaryDetails" sheetId="25" r:id="rId24"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="115">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -865,10 +867,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.453125" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1013,9 +1015,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1043,7 +1045,7 @@
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
@@ -1054,7 +1056,7 @@
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>36</v>
       </c>
       <c r="C4" t="s">
@@ -1065,11 +1067,11 @@
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1091,7 +1093,18 @@
         <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1100,12 +1113,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1159,7 +1169,7 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1170,7 +1180,7 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1178,21 +1188,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1201,12 +1200,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1229,6 +1227,72 @@
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1237,11 +1301,47 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1272,12 +1372,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1297,41 +1397,6 @@
       </c>
       <c r="B2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1343,12 +1408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1366,21 +1430,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1390,12 +1443,59 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1484,13 +1584,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1543,93 +1643,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="5">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1672,67 +1691,78 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2020</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1742,12 +1772,12 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1780,7 +1810,7 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1788,10 +1818,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4">
-        <v>987654321</v>
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1799,21 +1829,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1823,11 +1842,92 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>987654321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1936,14 +2036,126 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47B17BA-F990-45EB-8B28-07CF77412B89}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="3" width="25.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="8">
+        <v>20301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="8">
+        <v>7890368902</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2079,11 +2291,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,10 +2452,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2357,11 +2569,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449BFBB-D262-4256-B30F-8A2BD0B132FE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2451,14 +2672,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2546,10 +2767,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2598,102 +2819,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A9E19-6727-4E19-B817-63CFE77BDB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C73813-C1BE-467D-A534-0B51F544AB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="1296" windowWidth="17280" windowHeight="8880" firstSheet="20" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="107">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -171,12 +171,6 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldPrimaryRepFirstName__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepLastName__c</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
@@ -264,25 +258,7 @@
     <t>DC</t>
   </si>
   <si>
-    <t>fieldPrimaryRepAddress1__c</t>
-  </si>
-  <si>
     <t>Automation</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepCity__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepState__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepCountry__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepPhone__c</t>
   </si>
   <si>
     <t>Automation Representative</t>
@@ -397,7 +373,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +467,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -539,7 +521,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -583,6 +565,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -865,10 +848,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.453125" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+    <col min="3" max="3" width="51.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -890,7 +873,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -898,10 +881,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -909,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -920,10 +903,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -931,7 +914,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -942,10 +925,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -953,7 +936,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -964,10 +947,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -975,10 +958,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -986,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -997,7 +980,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1015,7 +998,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1077,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1088,10 +1071,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1102,9 +1085,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1167,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1178,7 +1161,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -1189,7 +1172,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1203,10 +1186,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1239,9 +1222,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1275,9 +1258,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1310,9 +1293,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1345,10 +1328,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1392,10 +1375,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1472,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1487,10 +1470,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1512,7 +1495,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1546,10 +1529,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1571,7 +1554,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1627,9 +1610,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1649,10 +1632,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1660,7 +1643,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1674,10 +1657,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1744,10 +1727,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1825,9 +1808,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1847,10 +1830,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1858,10 +1841,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1869,10 +1852,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1880,10 +1863,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1891,10 +1874,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1902,7 +1885,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C7" s="19">
         <v>20301</v>
@@ -1913,10 +1896,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1924,7 +1907,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>24</v>
@@ -1939,11 +1922,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1962,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>40</v>
@@ -1973,10 +1956,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1984,10 +1967,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1995,10 +1978,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2006,10 +1989,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2017,10 +2000,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2028,7 +2011,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2039,10 +2022,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2050,7 +2033,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2061,10 +2044,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2079,11 +2062,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2105,7 +2088,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2113,10 +2096,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2135,10 +2118,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2146,10 +2129,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2168,10 +2151,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2190,10 +2173,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2201,10 +2184,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2223,7 +2206,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>24</v>
@@ -2239,11 +2222,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2264,7 +2247,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>6</v>
@@ -2277,10 +2260,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -2290,10 +2273,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -2303,10 +2286,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2316,7 +2299,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2329,7 +2312,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2342,13 +2325,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2359,9 +2345,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2439,7 +2425,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2454,11 +2440,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2480,7 +2466,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2524,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2549,7 +2535,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2589,10 +2575,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2589,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -2665,7 +2651,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -2676,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2690,7 +2676,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A083106E-C044-425E-BB25-FEE6FA5D66C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57F245C-9349-4AD8-8A44-292BF2A1671D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santosh J\REI Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57F245C-9349-4AD8-8A44-292BF2A1671D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5956F15-B482-48C2-AC85-127F96E0F20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -269,9 +269,6 @@
     <t>fieldPrimaryRepAddress1__c</t>
   </si>
   <si>
-    <t>Automation</t>
-  </si>
-  <si>
     <t>fieldPrimaryRepCity__c</t>
   </si>
   <si>
@@ -393,6 +390,9 @@
   </si>
   <si>
     <t>EffectiveDate__c</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -867,10 +867,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -900,10 +900,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -911,7 +911,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -922,7 +922,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>59</v>
@@ -933,7 +933,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -944,10 +944,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -955,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -966,10 +966,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -977,7 +977,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>67</v>
@@ -988,7 +988,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -999,7 +999,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1017,7 +1017,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1115,7 +1115,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1202,9 +1202,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1303,10 +1303,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1339,9 +1339,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1375,9 +1375,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1410,9 +1410,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1445,10 +1445,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1492,10 +1492,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1587,10 +1587,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1646,9 +1646,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1668,7 +1668,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
@@ -1679,7 +1679,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1693,10 +1693,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1774,10 +1774,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1844,10 +1844,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1925,9 +1925,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5546875" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1950,7 +1950,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1972,7 +1972,7 @@
         <v>72</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1980,7 +1980,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>70</v>
@@ -1991,7 +1991,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>71</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="19">
         <v>20301</v>
@@ -2013,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>67</v>
@@ -2024,7 +2024,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>24</v>
@@ -2039,9 +2039,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47B17BA-F990-45EB-8B28-07CF77412B89}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2060,10 +2060,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2071,7 +2071,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>43</v>
@@ -2082,10 +2082,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2093,7 +2093,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>70</v>
@@ -2104,10 +2104,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2115,7 +2115,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="8">
         <v>20301</v>
@@ -2126,7 +2126,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>67</v>
@@ -2137,7 +2137,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="8">
         <v>7890368902</v>
@@ -2151,11 +2151,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2174,7 +2174,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>40</v>
@@ -2185,10 +2185,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2196,7 +2196,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>43</v>
@@ -2207,10 +2207,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2218,7 +2218,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>70</v>
@@ -2229,7 +2229,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>71</v>
@@ -2240,7 +2240,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2251,7 +2251,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>67</v>
@@ -2262,7 +2262,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2273,10 +2273,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2291,11 +2291,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2328,7 +2328,7 @@
         <v>57</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2452,10 +2452,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2476,7 +2476,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>6</v>
@@ -2489,7 +2489,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>69</v>
@@ -2502,7 +2502,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>70</v>
@@ -2515,10 +2515,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2528,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2541,7 +2541,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2554,7 +2554,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>
@@ -2571,7 +2571,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449BFBB-D262-4256-B30F-8A2BD0B132FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2580,9 +2580,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2675,11 +2675,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2770,7 +2770,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santosh\REIProject\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57F245C-9349-4AD8-8A44-292BF2A1671D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ED59F4-4C70-4248-88BA-F4535E6C7162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="107">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -173,12 +173,6 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldPrimaryRepFirstName__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepLastName__c</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
@@ -266,25 +260,7 @@
     <t>DC</t>
   </si>
   <si>
-    <t>fieldPrimaryRepAddress1__c</t>
-  </si>
-  <si>
     <t>Automation</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepCity__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepState__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepCountry__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepPhone__c</t>
   </si>
   <si>
     <t>Automation Representative</t>
@@ -867,10 +843,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -892,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -900,10 +876,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -911,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -922,10 +898,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -933,7 +909,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -944,10 +920,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -955,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -966,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -977,10 +953,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -988,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -999,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1017,7 +993,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1079,7 +1055,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1090,10 +1066,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1104,7 +1080,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1091,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1177,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1188,10 +1164,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1202,9 +1178,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1267,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1278,7 +1254,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -1289,7 +1265,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1303,10 +1279,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1339,9 +1315,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1375,9 +1351,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1410,9 +1386,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1445,10 +1421,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1492,10 +1468,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1572,7 +1548,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1587,10 +1563,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1612,7 +1588,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1646,9 +1622,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1668,10 +1644,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1679,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1693,10 +1669,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1718,7 +1694,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1774,10 +1750,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1844,10 +1820,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1925,9 +1901,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5546875" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1947,10 +1923,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1958,10 +1934,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1969,10 +1945,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1980,10 +1956,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1991,10 +1967,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2002,7 +1978,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C7" s="19">
         <v>20301</v>
@@ -2013,10 +1989,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2024,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>24</v>
@@ -2039,9 +2015,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47B17BA-F990-45EB-8B28-07CF77412B89}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2060,10 +2036,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2071,10 +2047,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2082,10 +2058,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2093,10 +2069,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2104,10 +2080,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2115,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C7" s="8">
         <v>20301</v>
@@ -2126,10 +2102,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2137,7 +2113,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C9" s="8">
         <v>7890368902</v>
@@ -2151,11 +2127,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2174,7 +2150,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>40</v>
@@ -2185,10 +2161,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2196,10 +2172,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2207,10 +2183,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2218,10 +2194,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2229,10 +2205,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2240,7 +2216,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2251,10 +2227,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2262,7 +2238,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2273,10 +2249,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2291,11 +2267,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2317,7 +2293,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2325,10 +2301,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2347,10 +2323,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2358,10 +2334,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2380,10 +2356,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2402,10 +2378,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2413,10 +2389,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2435,7 +2411,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>24</v>
@@ -2452,10 +2428,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2476,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>6</v>
@@ -2489,10 +2465,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -2502,10 +2478,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -2515,10 +2491,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2528,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2541,7 +2517,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2554,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>
@@ -2571,7 +2547,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449BFBB-D262-4256-B30F-8A2BD0B132FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2580,9 +2556,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2660,7 +2636,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2675,11 +2651,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2701,7 +2677,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2745,7 +2721,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2770,7 +2746,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2810,10 +2786,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santosh\REIProject\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ED59F4-4C70-4248-88BA-F4535E6C7162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700FC91-25E7-4C10-8DF3-C395017E583D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -278,9 +278,6 @@
     <t>SameAsOrganizationAddress__c</t>
   </si>
   <si>
-    <t>PaymentAddressLine1__c</t>
-  </si>
-  <si>
     <t>PaymentAddressCity__c</t>
   </si>
   <si>
@@ -369,6 +366,9 @@
   </si>
   <si>
     <t>EffectiveDate__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressline1__c</t>
   </si>
 </sst>
 </file>
@@ -876,10 +876,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -898,7 +898,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>57</v>
@@ -909,7 +909,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -920,10 +920,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -931,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -942,10 +942,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -953,7 +953,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>65</v>
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -975,7 +975,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1644,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
         <v>59</v>
@@ -1655,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>74</v>
@@ -1934,7 +1934,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>41</v>
@@ -1945,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>71</v>
@@ -1956,7 +1956,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>68</v>
@@ -1967,7 +1967,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>69</v>
@@ -1978,7 +1978,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="19">
         <v>20301</v>
@@ -1989,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>65</v>
@@ -2000,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>24</v>
@@ -2036,7 +2036,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>74</v>
@@ -2047,7 +2047,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>41</v>
@@ -2058,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>71</v>
@@ -2069,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>68</v>
@@ -2080,10 +2080,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2091,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="8">
         <v>20301</v>
@@ -2102,7 +2102,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>65</v>
@@ -2113,7 +2113,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" s="8">
         <v>7890368902</v>
@@ -2150,7 +2150,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>40</v>
@@ -2161,7 +2161,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>70</v>
@@ -2172,7 +2172,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>41</v>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>71</v>
@@ -2194,7 +2194,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>68</v>
@@ -2205,7 +2205,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>69</v>
@@ -2216,7 +2216,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2227,7 +2227,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>65</v>
@@ -2238,7 +2238,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2249,7 +2249,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>72</v>
@@ -2304,7 +2304,7 @@
         <v>55</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2465,7 +2465,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>67</v>
@@ -2478,7 +2478,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>68</v>
@@ -2491,10 +2491,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2504,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2517,7 +2517,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2530,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Merge_Org_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57F245C-9349-4AD8-8A44-292BF2A1671D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADED9E92-A039-4A6E-966C-B39ADA31B757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="111">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,33 +128,18 @@
     <t>USA: UNITED STATES</t>
   </si>
   <si>
-    <t>fieldOrganizationName__c</t>
-  </si>
-  <si>
-    <t>fieldOrganizationEstYear_NED__c</t>
-  </si>
-  <si>
-    <t>fieldOrganizationType__c</t>
-  </si>
-  <si>
     <t>Other Organization (Please Specify)</t>
   </si>
   <si>
     <t>Corporation or Professional Service Firm</t>
   </si>
   <si>
-    <t>fieldOrganizationStructureType_NED__c</t>
-  </si>
-  <si>
     <t>Not for Profit Organization</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>fieldPreferredLanguage__c</t>
-  </si>
-  <si>
     <t>fieldHaveEIN_NED__c</t>
   </si>
   <si>
@@ -164,21 +149,12 @@
     <t>fieldHaveNICRA_NED__c</t>
   </si>
   <si>
-    <t>fieldEINText__c</t>
-  </si>
-  <si>
     <t>IND: INDIA</t>
   </si>
   <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldPrimaryRepFirstName__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepLastName__c</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
@@ -200,12 +176,6 @@
     <t>Please explain why your organization is not incorporated or legally registered</t>
   </si>
   <si>
-    <t>fieldDoesOrgRegExpire_NED__c</t>
-  </si>
-  <si>
-    <t>fieldOrgValidThroughDate_NED__c</t>
-  </si>
-  <si>
     <t>India</t>
   </si>
   <si>
@@ -266,27 +236,9 @@
     <t>DC</t>
   </si>
   <si>
-    <t>fieldPrimaryRepAddress1__c</t>
-  </si>
-  <si>
     <t>Automation</t>
   </si>
   <si>
-    <t>fieldPrimaryRepCity__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepState__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepZipCode__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepCountry__c</t>
-  </si>
-  <si>
-    <t>fieldPrimaryRepPhone__c</t>
-  </si>
-  <si>
     <t>Automation Representative</t>
   </si>
   <si>
@@ -302,9 +254,6 @@
     <t>SameAsOrganizationAddress__c</t>
   </si>
   <si>
-    <t>PaymentAddressLine1__c</t>
-  </si>
-  <si>
     <t>PaymentAddressCity__c</t>
   </si>
   <si>
@@ -393,6 +342,45 @@
   </si>
   <si>
     <t>EffectiveDate__c</t>
+  </si>
+  <si>
+    <t>isBasedInUS_NED__c</t>
+  </si>
+  <si>
+    <t>HaveEIN_NED__c</t>
+  </si>
+  <si>
+    <t>EINText__c</t>
+  </si>
+  <si>
+    <t>is501c3TaxExemptOrg_NED__c</t>
+  </si>
+  <si>
+    <t>HaveNICRA_NED__c</t>
+  </si>
+  <si>
+    <t>OrganizationEstYear_NED__c</t>
+  </si>
+  <si>
+    <t>OrganizationType__c</t>
+  </si>
+  <si>
+    <t>OrganizationStructureType_NED__c</t>
+  </si>
+  <si>
+    <t>PreferredLanguage__c</t>
+  </si>
+  <si>
+    <t>DoesOrgRegExpire_NED__c</t>
+  </si>
+  <si>
+    <t>OrgValidThroughDate_NED__c</t>
+  </si>
+  <si>
+    <t>OrgNotLegalExplanation_NED__c</t>
+  </si>
+  <si>
+    <t>PaymentAddressline1__c</t>
   </si>
 </sst>
 </file>
@@ -867,10 +855,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
-    <col min="3" max="3" width="51.21875" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -892,7 +880,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -900,10 +888,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -911,7 +899,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>24</v>
@@ -922,10 +910,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -933,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>23</v>
@@ -944,10 +932,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -955,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>22</v>
@@ -966,10 +954,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -977,10 +965,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -988,7 +976,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C11" s="19">
         <v>20171</v>
@@ -999,7 +987,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>24</v>
@@ -1017,7 +1005,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1046,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1057,7 +1045,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1068,7 +1056,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1079,7 +1067,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1090,10 +1078,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1101,10 +1089,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1115,7 +1103,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="22.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1133,7 +1124,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -1144,7 +1135,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1155,7 +1146,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1166,7 +1157,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -1177,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1188,10 +1179,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1202,9 +1193,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1223,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -1234,7 +1225,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1245,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1256,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1267,7 +1258,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1278,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -1289,7 +1280,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1303,10 +1294,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1325,7 +1316,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -1339,9 +1330,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1375,9 +1366,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1396,7 +1387,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1410,9 +1401,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1445,10 +1436,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1467,7 +1458,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1492,10 +1483,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1572,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1587,10 +1578,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1609,10 +1600,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1620,7 +1611,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="C3" s="5">
         <v>2018</v>
@@ -1631,10 +1622,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1646,9 +1637,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1668,10 +1659,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1679,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1693,10 +1684,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1715,10 +1706,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1726,7 +1717,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="C3" s="5">
         <v>2020</v>
@@ -1737,10 +1728,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1748,10 +1739,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1759,10 +1750,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1774,10 +1765,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1796,7 +1787,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -1807,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1818,7 +1809,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1829,7 +1820,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1844,10 +1835,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1866,7 +1857,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -1877,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -1888,7 +1879,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>987654321</v>
@@ -1899,7 +1890,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -1910,7 +1901,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1925,9 +1916,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5546875" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1947,10 +1938,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1958,10 +1949,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1969,10 +1960,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1980,10 +1971,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1991,10 +1982,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2002,7 +1993,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C7" s="19">
         <v>20301</v>
@@ -2013,10 +2004,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2024,7 +2015,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>24</v>
@@ -2039,9 +2030,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47B17BA-F990-45EB-8B28-07CF77412B89}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="3" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2060,10 +2051,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2071,10 +2062,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2082,10 +2073,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2093,10 +2084,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2104,10 +2095,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2115,7 +2106,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C7" s="8">
         <v>20301</v>
@@ -2126,10 +2117,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2137,7 +2128,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C9" s="8">
         <v>7890368902</v>
@@ -2151,11 +2142,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2174,10 +2165,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2185,10 +2176,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2196,10 +2187,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2207,10 +2198,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2218,10 +2209,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2229,10 +2220,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2240,7 +2231,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C8" s="19">
         <v>20301</v>
@@ -2251,10 +2242,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2262,7 +2253,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>24</v>
@@ -2273,10 +2264,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2291,11 +2282,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2317,7 +2308,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2325,10 +2316,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2347,10 +2338,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2358,10 +2349,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2380,10 +2371,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2402,10 +2393,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2413,10 +2404,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2435,7 +2426,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>24</v>
@@ -2452,10 +2443,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2476,7 +2467,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>6</v>
@@ -2489,10 +2480,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -2502,10 +2493,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -2515,10 +2506,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2528,7 +2519,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C6" s="19">
         <v>20301</v>
@@ -2541,7 +2532,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C7" s="19">
         <v>1234</v>
@@ -2554,7 +2545,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>24</v>
@@ -2571,7 +2562,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6449BFBB-D262-4256-B30F-8A2BD0B132FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2580,9 +2571,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2627,7 +2618,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2660,7 +2651,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2675,11 +2666,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2701,7 +2692,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2745,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2770,7 +2761,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2810,10 +2801,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
